--- a/SPECTRE1_Pricing_Matrix.xlsx
+++ b/SPECTRE1_Pricing_Matrix.xlsx
@@ -168,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,7 +226,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1101,1138 +1100,1138 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-53 Rev 5 High baseline, tailored for DoW systems</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n"/>
-      <c r="D5" s="45" t="n"/>
-      <c r="E5" s="45" t="n"/>
-      <c r="F5" s="45" t="n"/>
-      <c r="G5" s="45" t="n"/>
-      <c r="H5" s="45" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="44" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-223 (HPC Security)</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
-      <c r="G6" s="45" t="n"/>
-      <c r="H6" s="45" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-207 (Zero Trust Architecture)</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n"/>
-      <c r="D7" s="45" t="n"/>
-      <c r="E7" s="45" t="n"/>
-      <c r="F7" s="45" t="n"/>
-      <c r="G7" s="45" t="n"/>
-      <c r="H7" s="45" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-216 (Vulnerability Disclosure)</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="45" t="n"/>
-      <c r="G8" s="45" t="n"/>
-      <c r="H8" s="45" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B9" s="44" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-193 (Platform Firmware Resiliency)</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n"/>
-      <c r="D9" s="45" t="n"/>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="45" t="n"/>
-      <c r="G9" s="45" t="n"/>
-      <c r="H9" s="45" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>NIST SP 800-161 (Cybersecurity Supply Chain Risk)</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="45" t="n"/>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="45" t="n"/>
-      <c r="G10" s="45" t="n"/>
-      <c r="H10" s="45" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>FIPS 140-3 and SP 800-52 / 800-57 / 800-131A for cryptography</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="45" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="45" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="44" t="n"/>
+      <c r="H11" s="44" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Data encrypted at rest</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="45" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="45" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="44" t="n"/>
+      <c r="H12" s="44" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>Data encrypted in transit where technically feasible; describe exceptions</t>
         </is>
       </c>
-      <c r="C13" s="45" t="n"/>
-      <c r="D13" s="45" t="n"/>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="45" t="n"/>
-      <c r="G13" s="45" t="n"/>
-      <c r="H13" s="45" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>3.1.4</t>
         </is>
       </c>
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>All inter-cabinet cables optical or shielded twisted pair; intra-node optical preferred</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="45" t="n"/>
-      <c r="E14" s="45" t="n"/>
-      <c r="F14" s="45" t="n"/>
-      <c r="G14" s="45" t="n"/>
-      <c r="H14" s="45" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>3.1.5</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>FIPS 140-3 compliant and/or NSA-approved cryptographic algorithms</t>
         </is>
       </c>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="45" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="45" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>3.1.6</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>TAA compliance — all hardware, software and integrated components (19 U.S.C. 2501–2581)</t>
         </is>
       </c>
-      <c r="C16" s="45" t="n"/>
-      <c r="D16" s="45" t="n"/>
-      <c r="E16" s="45" t="n"/>
-      <c r="F16" s="45" t="n"/>
-      <c r="G16" s="45" t="n"/>
-      <c r="H16" s="45" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="44" t="n"/>
+      <c r="H16" s="44" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>3.1.7</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>System capable of full ATO under RMF once transitioned to DoW; supply all supporting artifacts</t>
         </is>
       </c>
-      <c r="C17" s="45" t="n"/>
-      <c r="D17" s="45" t="n"/>
-      <c r="E17" s="45" t="n"/>
-      <c r="F17" s="45" t="n"/>
-      <c r="G17" s="45" t="n"/>
-      <c r="H17" s="45" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>3.1.8</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Active software support for full operational lifetime; Critical/High CVSS v4 fixes within 30 days</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
-      <c r="G18" s="45" t="n"/>
-      <c r="H18" s="45" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>3.1.9</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>SCRM strategy aligned to NIST SE-1 through SE-3, with register, scorecards and authenticity logs</t>
         </is>
       </c>
-      <c r="C19" s="45" t="n"/>
-      <c r="D19" s="45" t="n"/>
-      <c r="E19" s="45" t="n"/>
-      <c r="F19" s="45" t="n"/>
-      <c r="G19" s="45" t="n"/>
-      <c r="H19" s="45" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="44" t="n"/>
+      <c r="H19" s="44" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="42" t="inlineStr">
         <is>
           <t>3.1.10</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Secure boot and firmware controls; DISA STIG and SCAP compatibility; secure OS/hypervisor config</t>
         </is>
       </c>
-      <c r="C20" s="45" t="n"/>
-      <c r="D20" s="45" t="n"/>
-      <c r="E20" s="45" t="n"/>
-      <c r="F20" s="45" t="n"/>
-      <c r="G20" s="45" t="n"/>
-      <c r="H20" s="45" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>3.1.11</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>All personnel — staff, vendors and subcontractors — are US citizens</t>
         </is>
       </c>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="45" t="n"/>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="45" t="n"/>
-      <c r="G21" s="45" t="n"/>
-      <c r="H21" s="45" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="44" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>3.1.12</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Formal secure SDLC with security checkpoints; version control, RBAC, audit trails</t>
         </is>
       </c>
-      <c r="C22" s="45" t="n"/>
-      <c r="D22" s="45" t="n"/>
-      <c r="E22" s="45" t="n"/>
-      <c r="F22" s="45" t="n"/>
-      <c r="G22" s="45" t="n"/>
-      <c r="H22" s="45" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="44" t="n"/>
+      <c r="G22" s="44" t="n"/>
+      <c r="H22" s="44" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>3.1.13</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>SCIS, SSP, CM Plan, IR Plan delivered at system delivery</t>
         </is>
       </c>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="45" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="45" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+      <c r="F23" s="44" t="n"/>
+      <c r="G23" s="44" t="n"/>
+      <c r="H23" s="44" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>3.1.14</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>Pre-handoff audit: STIG/SCAP scans, AU-family logging validation, test procedures</t>
         </is>
       </c>
-      <c r="C24" s="45" t="n"/>
-      <c r="D24" s="45" t="n"/>
-      <c r="E24" s="45" t="n"/>
-      <c r="F24" s="45" t="n"/>
-      <c r="G24" s="45" t="n"/>
-      <c r="H24" s="45" t="n"/>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="44" t="n"/>
+      <c r="H24" s="44" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>SSU modular building blocks</t>
         </is>
       </c>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="45" t="n"/>
-      <c r="F25" s="45" t="n"/>
-      <c r="G25" s="45" t="n"/>
-      <c r="H25" s="45" t="n"/>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="44" t="n"/>
+      <c r="H25" s="44" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Highly available: redundant chassis components, power and software</t>
         </is>
       </c>
-      <c r="C26" s="45" t="n"/>
-      <c r="D26" s="45" t="n"/>
-      <c r="E26" s="45" t="n"/>
-      <c r="F26" s="45" t="n"/>
-      <c r="G26" s="45" t="n"/>
-      <c r="H26" s="45" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="44" t="n"/>
+      <c r="H26" s="44" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>ECC DIMMs of a uniform FRU type</t>
         </is>
       </c>
-      <c r="C27" s="45" t="n"/>
-      <c r="D27" s="45" t="n"/>
-      <c r="E27" s="45" t="n"/>
-      <c r="F27" s="45" t="n"/>
-      <c r="G27" s="45" t="n"/>
-      <c r="H27" s="45" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
+      <c r="H27" s="44" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="43" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B28" s="44" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>HSN integration — 400 GbE or equivalent (UE, Slingshot, InfiniBand)</t>
         </is>
       </c>
-      <c r="C28" s="45" t="n"/>
-      <c r="D28" s="45" t="n"/>
-      <c r="E28" s="45" t="n"/>
-      <c r="F28" s="45" t="n"/>
-      <c r="G28" s="45" t="n"/>
-      <c r="H28" s="45" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="44" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>PMR/CMR HDDs only — HAMR, MAMR and Shingled not permitted</t>
         </is>
       </c>
-      <c r="C29" s="45" t="n"/>
-      <c r="D29" s="45" t="n"/>
-      <c r="E29" s="45" t="n"/>
-      <c r="F29" s="45" t="n"/>
-      <c r="G29" s="45" t="n"/>
-      <c r="H29" s="45" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="44" t="n"/>
+      <c r="H29" s="44" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>FIPS 140-2 certified or 140-3 compliant self-encrypting drives on all storage media</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="45" t="n"/>
-      <c r="H30" s="45" t="n"/>
+      <c r="C30" s="44" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="44" t="n"/>
+      <c r="G30" s="44" t="n"/>
+      <c r="H30" s="44" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="43" t="inlineStr">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>Hot-swappable media, fans and power supplies where feasible</t>
         </is>
       </c>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="45" t="n"/>
-      <c r="H31" s="45" t="n"/>
+      <c r="C31" s="44" t="n"/>
+      <c r="D31" s="44" t="n"/>
+      <c r="E31" s="44" t="n"/>
+      <c r="F31" s="44" t="n"/>
+      <c r="G31" s="44" t="n"/>
+      <c r="H31" s="44" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>Base proposal occupies 50% of production floorspace; remainder priced as SSU options</t>
         </is>
       </c>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="45" t="n"/>
-      <c r="E32" s="45" t="n"/>
-      <c r="F32" s="45" t="n"/>
-      <c r="G32" s="45" t="n"/>
-      <c r="H32" s="45" t="n"/>
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+      <c r="F32" s="44" t="n"/>
+      <c r="G32" s="44" t="n"/>
+      <c r="H32" s="44" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>3.2.1</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>Two identical Test &amp; Development Systems, each fully functional and standalone</t>
         </is>
       </c>
-      <c r="C33" s="45" t="n"/>
-      <c r="D33" s="45" t="n"/>
-      <c r="E33" s="45" t="n"/>
-      <c r="F33" s="45" t="n"/>
-      <c r="G33" s="45" t="n"/>
-      <c r="H33" s="45" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="44" t="n"/>
+      <c r="G33" s="44" t="n"/>
+      <c r="H33" s="44" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>Single POSIX-compliant namespace</t>
         </is>
       </c>
-      <c r="C34" s="45" t="n"/>
-      <c r="D34" s="45" t="n"/>
-      <c r="E34" s="45" t="n"/>
-      <c r="F34" s="45" t="n"/>
-      <c r="G34" s="45" t="n"/>
-      <c r="H34" s="45" t="n"/>
+      <c r="C34" s="44" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="44" t="n"/>
+      <c r="F34" s="44" t="n"/>
+      <c r="G34" s="44" t="n"/>
+      <c r="H34" s="44" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>Up to 120 network endpoints to the compute-fabric HSN</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n"/>
-      <c r="D35" s="45" t="n"/>
-      <c r="E35" s="45" t="n"/>
-      <c r="F35" s="45" t="n"/>
-      <c r="G35" s="45" t="n"/>
-      <c r="H35" s="45" t="n"/>
+      <c r="C35" s="44" t="n"/>
+      <c r="D35" s="44" t="n"/>
+      <c r="E35" s="44" t="n"/>
+      <c r="F35" s="44" t="n"/>
+      <c r="G35" s="44" t="n"/>
+      <c r="H35" s="44" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Between 150 PB and 250 PB usable space</t>
         </is>
       </c>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="45" t="n"/>
-      <c r="E36" s="45" t="n"/>
-      <c r="F36" s="45" t="n"/>
-      <c r="G36" s="45" t="n"/>
-      <c r="H36" s="45" t="n"/>
+      <c r="C36" s="44" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="44" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="44" t="n"/>
+      <c r="H36" s="44" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>3.2.3</t>
         </is>
       </c>
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>Data path and control plane do not require container orchestrators (preference)</t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="45" t="n"/>
-      <c r="H37" s="45" t="n"/>
+      <c r="C37" s="44" t="n"/>
+      <c r="D37" s="44" t="n"/>
+      <c r="E37" s="44" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="44" t="n"/>
+      <c r="H37" s="44" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>Namespace, per-SSU and per-component bandwidth, IOPS and latency; block and client level</t>
         </is>
       </c>
-      <c r="C38" s="45" t="n"/>
-      <c r="D38" s="45" t="n"/>
-      <c r="E38" s="45" t="n"/>
-      <c r="F38" s="45" t="n"/>
-      <c r="G38" s="45" t="n"/>
-      <c r="H38" s="45" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
+      <c r="H38" s="44" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="44" t="inlineStr">
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>Complete test parameters, configurations and methodologies disclosed</t>
         </is>
       </c>
-      <c r="C39" s="45" t="n"/>
-      <c r="D39" s="45" t="n"/>
-      <c r="E39" s="45" t="n"/>
-      <c r="F39" s="45" t="n"/>
-      <c r="G39" s="45" t="n"/>
-      <c r="H39" s="45" t="n"/>
+      <c r="C39" s="44" t="n"/>
+      <c r="D39" s="44" t="n"/>
+      <c r="E39" s="44" t="n"/>
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="44" t="n"/>
+      <c r="H39" s="44" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="43" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Acceptance against a namespace artificially aged to ~70% utilization</t>
         </is>
       </c>
-      <c r="C40" s="45" t="n"/>
-      <c r="D40" s="45" t="n"/>
-      <c r="E40" s="45" t="n"/>
-      <c r="F40" s="45" t="n"/>
-      <c r="G40" s="45" t="n"/>
-      <c r="H40" s="45" t="n"/>
+      <c r="C40" s="44" t="n"/>
+      <c r="D40" s="44" t="n"/>
+      <c r="E40" s="44" t="n"/>
+      <c r="F40" s="44" t="n"/>
+      <c r="G40" s="44" t="n"/>
+      <c r="H40" s="44" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="43" t="inlineStr">
+      <c r="A41" s="42" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B41" s="44" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>End-to-end network bandwidth testing</t>
         </is>
       </c>
-      <c r="C41" s="45" t="n"/>
-      <c r="D41" s="45" t="n"/>
-      <c r="E41" s="45" t="n"/>
-      <c r="F41" s="45" t="n"/>
-      <c r="G41" s="45" t="n"/>
-      <c r="H41" s="45" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="44" t="n"/>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+      <c r="G41" s="44" t="n"/>
+      <c r="H41" s="44" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="43" t="inlineStr">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>IOR and mdtest compared against published specifications</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
-      <c r="G42" s="45" t="n"/>
-      <c r="H42" s="45" t="n"/>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+      <c r="G42" s="44" t="n"/>
+      <c r="H42" s="44" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B43" s="44" t="inlineStr">
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>Redundancy, fault tolerance and peripheral/torque validation</t>
         </is>
       </c>
-      <c r="C43" s="45" t="n"/>
-      <c r="D43" s="45" t="n"/>
-      <c r="E43" s="45" t="n"/>
-      <c r="F43" s="45" t="n"/>
-      <c r="G43" s="45" t="n"/>
-      <c r="H43" s="45" t="n"/>
+      <c r="C43" s="44" t="n"/>
+      <c r="D43" s="44" t="n"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="44" t="n"/>
+      <c r="G43" s="44" t="n"/>
+      <c r="H43" s="44" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="43" t="inlineStr">
+      <c r="A44" s="42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B44" s="44" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>Quarterly system updates and security patches at minimum</t>
         </is>
       </c>
-      <c r="C44" s="45" t="n"/>
-      <c r="D44" s="45" t="n"/>
-      <c r="E44" s="45" t="n"/>
-      <c r="F44" s="45" t="n"/>
-      <c r="G44" s="45" t="n"/>
-      <c r="H44" s="45" t="n"/>
+      <c r="C44" s="44" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="n"/>
+      <c r="G44" s="44" t="n"/>
+      <c r="H44" s="44" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="43" t="inlineStr">
+      <c r="A45" s="42" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>Four-year maintenance base, with 5th-year, 6th-year and deferred options</t>
         </is>
       </c>
-      <c r="C45" s="45" t="n"/>
-      <c r="D45" s="45" t="n"/>
-      <c r="E45" s="45" t="n"/>
-      <c r="F45" s="45" t="n"/>
-      <c r="G45" s="45" t="n"/>
-      <c r="H45" s="45" t="n"/>
+      <c r="C45" s="44" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="44" t="n"/>
+      <c r="F45" s="44" t="n"/>
+      <c r="G45" s="44" t="n"/>
+      <c r="H45" s="44" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="43" t="inlineStr">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>On-site parts cache sustaining two weeks of repairs with no refresh, incl. hot spare nodes</t>
         </is>
       </c>
-      <c r="C46" s="45" t="n"/>
-      <c r="D46" s="45" t="n"/>
-      <c r="E46" s="45" t="n"/>
-      <c r="F46" s="45" t="n"/>
-      <c r="G46" s="45" t="n"/>
-      <c r="H46" s="45" t="n"/>
+      <c r="C46" s="44" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="44" t="n"/>
+      <c r="F46" s="44" t="n"/>
+      <c r="G46" s="44" t="n"/>
+      <c r="H46" s="44" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>No hardware leaves the site — destroyed by the Company</t>
         </is>
       </c>
-      <c r="C47" s="45" t="n"/>
-      <c r="D47" s="45" t="n"/>
-      <c r="E47" s="45" t="n"/>
-      <c r="F47" s="45" t="n"/>
-      <c r="G47" s="45" t="n"/>
-      <c r="H47" s="45" t="n"/>
+      <c r="C47" s="44" t="n"/>
+      <c r="D47" s="44" t="n"/>
+      <c r="E47" s="44" t="n"/>
+      <c r="F47" s="44" t="n"/>
+      <c r="G47" s="44" t="n"/>
+      <c r="H47" s="44" t="n"/>
     </row>
     <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>All licenses provided: RHEL, file system, and HA functionality</t>
         </is>
       </c>
-      <c r="C48" s="45" t="n"/>
-      <c r="D48" s="45" t="n"/>
-      <c r="E48" s="45" t="n"/>
-      <c r="F48" s="45" t="n"/>
-      <c r="G48" s="45" t="n"/>
-      <c r="H48" s="45" t="n"/>
+      <c r="C48" s="44" t="n"/>
+      <c r="D48" s="44" t="n"/>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="44" t="n"/>
+      <c r="G48" s="44" t="n"/>
+      <c r="H48" s="44" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>On-site System Software Analyst with DOE Q-clearance, separately priced</t>
         </is>
       </c>
-      <c r="C49" s="45" t="n"/>
-      <c r="D49" s="45" t="n"/>
-      <c r="E49" s="45" t="n"/>
-      <c r="F49" s="45" t="n"/>
-      <c r="G49" s="45" t="n"/>
-      <c r="H49" s="45" t="n"/>
+      <c r="C49" s="44" t="n"/>
+      <c r="D49" s="44" t="n"/>
+      <c r="E49" s="44" t="n"/>
+      <c r="F49" s="44" t="n"/>
+      <c r="G49" s="44" t="n"/>
+      <c r="H49" s="44" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="43" t="inlineStr">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B50" s="44" t="inlineStr">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>Interface documentation, procedures and drawings</t>
         </is>
       </c>
-      <c r="C50" s="45" t="n"/>
-      <c r="D50" s="45" t="n"/>
-      <c r="E50" s="45" t="n"/>
-      <c r="F50" s="45" t="n"/>
-      <c r="G50" s="45" t="n"/>
-      <c r="H50" s="45" t="n"/>
+      <c r="C50" s="44" t="n"/>
+      <c r="D50" s="44" t="n"/>
+      <c r="E50" s="44" t="n"/>
+      <c r="F50" s="44" t="n"/>
+      <c r="G50" s="44" t="n"/>
+      <c r="H50" s="44" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="43" t="inlineStr">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>Delivery, installation and integration; handling and disposition of all materials</t>
         </is>
       </c>
-      <c r="C51" s="45" t="n"/>
-      <c r="D51" s="45" t="n"/>
-      <c r="E51" s="45" t="n"/>
-      <c r="F51" s="45" t="n"/>
-      <c r="G51" s="45" t="n"/>
-      <c r="H51" s="45" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="44" t="n"/>
+      <c r="E51" s="44" t="n"/>
+      <c r="F51" s="44" t="n"/>
+      <c r="G51" s="44" t="n"/>
+      <c r="H51" s="44" t="n"/>
     </row>
     <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="43" t="inlineStr">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B52" s="44" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>17 x 600 mm racks (16 production + 1 TDS), 50U, overhead connectivity only, no raised floor</t>
         </is>
       </c>
-      <c r="C52" s="45" t="n"/>
-      <c r="D52" s="45" t="n"/>
-      <c r="E52" s="45" t="n"/>
-      <c r="F52" s="45" t="n"/>
-      <c r="G52" s="45" t="n"/>
-      <c r="H52" s="45" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="44" t="n"/>
+      <c r="F52" s="44" t="n"/>
+      <c r="G52" s="44" t="n"/>
+      <c r="H52" s="44" t="n"/>
     </row>
     <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="43" t="inlineStr">
+      <c r="A53" s="42" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B53" s="44" t="inlineStr">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>Cluster management and 5300-DC TDS in separate cabinets within the space limit</t>
         </is>
       </c>
-      <c r="C53" s="45" t="n"/>
-      <c r="D53" s="45" t="n"/>
-      <c r="E53" s="45" t="n"/>
-      <c r="F53" s="45" t="n"/>
-      <c r="G53" s="45" t="n"/>
-      <c r="H53" s="45" t="n"/>
+      <c r="C53" s="44" t="n"/>
+      <c r="D53" s="44" t="n"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="44" t="n"/>
+      <c r="G53" s="44" t="n"/>
+      <c r="H53" s="44" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="43" t="inlineStr">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>3-phase 60 A 208 VAC IEC60309, dual-fed diverse (utility + UPS)</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
-      <c r="G54" s="45" t="n"/>
-      <c r="H54" s="45" t="n"/>
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="44" t="n"/>
+      <c r="F54" s="44" t="n"/>
+      <c r="G54" s="44" t="n"/>
+      <c r="H54" s="44" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="43" t="inlineStr">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B55" s="44" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>Non-pocket in-rack PDUs: port-switchable, monitorable, watertight sleeve, outlet locking</t>
         </is>
       </c>
-      <c r="C55" s="45" t="n"/>
-      <c r="D55" s="45" t="n"/>
-      <c r="E55" s="45" t="n"/>
-      <c r="F55" s="45" t="n"/>
-      <c r="G55" s="45" t="n"/>
-      <c r="H55" s="45" t="n"/>
+      <c r="C55" s="44" t="n"/>
+      <c r="D55" s="44" t="n"/>
+      <c r="E55" s="44" t="n"/>
+      <c r="F55" s="44" t="n"/>
+      <c r="G55" s="44" t="n"/>
+      <c r="H55" s="44" t="n"/>
     </row>
     <row r="56" ht="26" customHeight="1">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B56" s="44" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>Total power not to exceed 275 kW</t>
         </is>
       </c>
-      <c r="C56" s="45" t="n"/>
-      <c r="D56" s="45" t="n"/>
-      <c r="E56" s="45" t="n"/>
-      <c r="F56" s="45" t="n"/>
-      <c r="G56" s="45" t="n"/>
-      <c r="H56" s="45" t="n"/>
+      <c r="C56" s="44" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="44" t="n"/>
+      <c r="F56" s="44" t="n"/>
+      <c r="G56" s="44" t="n"/>
+      <c r="H56" s="44" t="n"/>
     </row>
     <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="43" t="inlineStr">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B57" s="44" t="inlineStr">
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>RDHX per cabinet: top-fed, fail-closed valves, 1in sanitary connections</t>
         </is>
       </c>
-      <c r="C57" s="45" t="n"/>
-      <c r="D57" s="45" t="n"/>
-      <c r="E57" s="45" t="n"/>
-      <c r="F57" s="45" t="n"/>
-      <c r="G57" s="45" t="n"/>
-      <c r="H57" s="45" t="n"/>
+      <c r="C57" s="44" t="n"/>
+      <c r="D57" s="44" t="n"/>
+      <c r="E57" s="44" t="n"/>
+      <c r="F57" s="44" t="n"/>
+      <c r="G57" s="44" t="n"/>
+      <c r="H57" s="44" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="43" t="inlineStr">
+      <c r="A58" s="42" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B58" s="44" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>RDHX flow &lt;= 11 gpm each, supply water 60–68 F, room neutral at 75 F rack inlet</t>
         </is>
       </c>
-      <c r="C58" s="45" t="n"/>
-      <c r="D58" s="45" t="n"/>
-      <c r="E58" s="45" t="n"/>
-      <c r="F58" s="45" t="n"/>
-      <c r="G58" s="45" t="n"/>
-      <c r="H58" s="45" t="n"/>
+      <c r="C58" s="44" t="n"/>
+      <c r="D58" s="44" t="n"/>
+      <c r="E58" s="44" t="n"/>
+      <c r="F58" s="44" t="n"/>
+      <c r="G58" s="44" t="n"/>
+      <c r="H58" s="44" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="43" t="inlineStr">
+      <c r="A59" s="42" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B59" s="44" t="inlineStr">
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>BACnet/IP monitoring; rack-level leak detection with shut-down capability</t>
         </is>
       </c>
-      <c r="C59" s="45" t="n"/>
-      <c r="D59" s="45" t="n"/>
-      <c r="E59" s="45" t="n"/>
-      <c r="F59" s="45" t="n"/>
-      <c r="G59" s="45" t="n"/>
-      <c r="H59" s="45" t="n"/>
+      <c r="C59" s="44" t="n"/>
+      <c r="D59" s="44" t="n"/>
+      <c r="E59" s="44" t="n"/>
+      <c r="F59" s="44" t="n"/>
+      <c r="G59" s="44" t="n"/>
+      <c r="H59" s="44" t="n"/>
     </row>
     <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="A60" s="42" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B60" s="44" t="inlineStr">
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>Check valve on return, control valve on supply; &lt;5% parasitic heat during maintenance</t>
         </is>
       </c>
-      <c r="C60" s="45" t="n"/>
-      <c r="D60" s="45" t="n"/>
-      <c r="E60" s="45" t="n"/>
-      <c r="F60" s="45" t="n"/>
-      <c r="G60" s="45" t="n"/>
-      <c r="H60" s="45" t="n"/>
+      <c r="C60" s="44" t="n"/>
+      <c r="D60" s="44" t="n"/>
+      <c r="E60" s="44" t="n"/>
+      <c r="F60" s="44" t="n"/>
+      <c r="G60" s="44" t="n"/>
+      <c r="H60" s="44" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="43" t="inlineStr">
+      <c r="A61" s="42" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B61" s="44" t="inlineStr">
+      <c r="B61" s="43" t="inlineStr">
         <is>
           <t>Offeror delivers, uncrates, stages, mounts and connects RDHXs and removes packaging</t>
         </is>
       </c>
-      <c r="C61" s="45" t="n"/>
-      <c r="D61" s="45" t="n"/>
-      <c r="E61" s="45" t="n"/>
-      <c r="F61" s="45" t="n"/>
-      <c r="G61" s="45" t="n"/>
-      <c r="H61" s="45" t="n"/>
+      <c r="C61" s="44" t="n"/>
+      <c r="D61" s="44" t="n"/>
+      <c r="E61" s="44" t="n"/>
+      <c r="F61" s="44" t="n"/>
+      <c r="G61" s="44" t="n"/>
+      <c r="H61" s="44" t="n"/>
     </row>
     <row r="62" ht="26" customHeight="1">
-      <c r="A62" s="43" t="inlineStr">
+      <c r="A62" s="42" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B62" s="44" t="inlineStr">
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>Executive Liaison and Technical Project Manager identified</t>
         </is>
       </c>
-      <c r="C62" s="45" t="n"/>
-      <c r="D62" s="45" t="n"/>
-      <c r="E62" s="45" t="n"/>
-      <c r="F62" s="45" t="n"/>
-      <c r="G62" s="45" t="n"/>
-      <c r="H62" s="45" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
+      <c r="F62" s="44" t="n"/>
+      <c r="G62" s="44" t="n"/>
+      <c r="H62" s="44" t="n"/>
     </row>
     <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="43" t="inlineStr">
+      <c r="A63" s="42" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B63" s="44" t="inlineStr">
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>Delivery/installation/integration/acceptance schedule aligned to §1 milestones</t>
         </is>
       </c>
-      <c r="C63" s="45" t="n"/>
-      <c r="D63" s="45" t="n"/>
-      <c r="E63" s="45" t="n"/>
-      <c r="F63" s="45" t="n"/>
-      <c r="G63" s="45" t="n"/>
-      <c r="H63" s="45" t="n"/>
+      <c r="C63" s="44" t="n"/>
+      <c r="D63" s="44" t="n"/>
+      <c r="E63" s="44" t="n"/>
+      <c r="F63" s="44" t="n"/>
+      <c r="G63" s="44" t="n"/>
+      <c r="H63" s="44" t="n"/>
     </row>
     <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="43" t="inlineStr">
+      <c r="A64" s="42" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B64" s="44" t="inlineStr">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>Site Preparation Plan within 30 days of award</t>
         </is>
       </c>
-      <c r="C64" s="45" t="n"/>
-      <c r="D64" s="45" t="n"/>
-      <c r="E64" s="45" t="n"/>
-      <c r="F64" s="45" t="n"/>
-      <c r="G64" s="45" t="n"/>
-      <c r="H64" s="45" t="n"/>
+      <c r="C64" s="44" t="n"/>
+      <c r="D64" s="44" t="n"/>
+      <c r="E64" s="44" t="n"/>
+      <c r="F64" s="44" t="n"/>
+      <c r="G64" s="44" t="n"/>
+      <c r="H64" s="44" t="n"/>
     </row>
     <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="43" t="inlineStr">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="B65" s="44" t="inlineStr">
+      <c r="B65" s="43" t="inlineStr">
         <is>
           <t>Maintenance &amp; Support Plan at least 30 days before first delivery</t>
         </is>
       </c>
-      <c r="C65" s="45" t="n"/>
-      <c r="D65" s="45" t="n"/>
-      <c r="E65" s="45" t="n"/>
-      <c r="F65" s="45" t="n"/>
-      <c r="G65" s="45" t="n"/>
-      <c r="H65" s="45" t="n"/>
+      <c r="C65" s="44" t="n"/>
+      <c r="D65" s="44" t="n"/>
+      <c r="E65" s="44" t="n"/>
+      <c r="F65" s="44" t="n"/>
+      <c r="G65" s="44" t="n"/>
+      <c r="H65" s="44" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="43" t="inlineStr">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B66" s="44" t="inlineStr">
+      <c r="B66" s="43" t="inlineStr">
         <is>
           <t>Acceptance: hardware phase, functionality walk-through, performance test, stability test</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
-      <c r="G66" s="45" t="n"/>
-      <c r="H66" s="45" t="n"/>
+      <c r="C66" s="44" t="n"/>
+      <c r="D66" s="44" t="n"/>
+      <c r="E66" s="44" t="n"/>
+      <c r="F66" s="44" t="n"/>
+      <c r="G66" s="44" t="n"/>
+      <c r="H66" s="44" t="n"/>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="43" t="inlineStr">
+      <c r="A67" s="42" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="B67" s="44" t="inlineStr">
+      <c r="B67" s="43" t="inlineStr">
         <is>
           <t>Benchmarks executable from a non-privileged account</t>
         </is>
       </c>
-      <c r="C67" s="45" t="n"/>
-      <c r="D67" s="45" t="n"/>
-      <c r="E67" s="45" t="n"/>
-      <c r="F67" s="45" t="n"/>
-      <c r="G67" s="45" t="n"/>
-      <c r="H67" s="45" t="n"/>
+      <c r="C67" s="44" t="n"/>
+      <c r="D67" s="44" t="n"/>
+      <c r="E67" s="44" t="n"/>
+      <c r="F67" s="44" t="n"/>
+      <c r="G67" s="44" t="n"/>
+      <c r="H67" s="44" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="24" t="inlineStr">
@@ -2709,15 +2708,15 @@
       </c>
       <c r="B24" s="14" t="n"/>
       <c r="C24" s="20">
-        <f>'Services &amp; Deliverables'!$E$28</f>
+        <f>'Services &amp; Deliverables'!$E$30</f>
         <v/>
       </c>
       <c r="D24" s="20">
-        <f>'Services &amp; Deliverables'!$E$28</f>
+        <f>'Services &amp; Deliverables'!$E$30</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>'Services &amp; Deliverables'!$E$28</f>
+        <f>'Services &amp; Deliverables'!$E$30</f>
         <v/>
       </c>
     </row>
@@ -2729,15 +2728,15 @@
       </c>
       <c r="B25" s="14" t="n"/>
       <c r="C25" s="20">
-        <f>'Support &amp; Maintenance'!$I$22</f>
+        <f>SUM('Support &amp; Maintenance'!$D$22:$G$22)-SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f>'Support &amp; Maintenance'!$I$22</f>
+        <f>SUM('Support &amp; Maintenance'!$D$22:$G$22)-SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>'Support &amp; Maintenance'!$I$22</f>
+        <f>SUM('Support &amp; Maintenance'!$D$22:$G$22)-SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
     </row>
@@ -2749,15 +2748,15 @@
       </c>
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="20">
-        <f>'Support &amp; Maintenance'!$G$22</f>
+        <f>'Support &amp; Maintenance'!$H$22-'Support &amp; Maintenance'!$H$18</f>
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>'Support &amp; Maintenance'!$G$22</f>
+        <f>'Support &amp; Maintenance'!$H$22-'Support &amp; Maintenance'!$H$18</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>'Support &amp; Maintenance'!$G$22</f>
+        <f>'Support &amp; Maintenance'!$H$22-'Support &amp; Maintenance'!$H$18</f>
         <v/>
       </c>
     </row>
@@ -2769,15 +2768,15 @@
       </c>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="20">
-        <f>'Support &amp; Maintenance'!$H$22</f>
+        <f>'Support &amp; Maintenance'!$I$22-'Support &amp; Maintenance'!$I$18</f>
         <v/>
       </c>
       <c r="D27" s="20">
-        <f>'Support &amp; Maintenance'!$H$22</f>
+        <f>'Support &amp; Maintenance'!$I$22-'Support &amp; Maintenance'!$I$18</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>'Support &amp; Maintenance'!$H$22</f>
+        <f>'Support &amp; Maintenance'!$I$22-'Support &amp; Maintenance'!$I$18</f>
         <v/>
       </c>
     </row>
@@ -2789,15 +2788,15 @@
       </c>
       <c r="B28" s="14" t="n"/>
       <c r="C28" s="20">
-        <f>'Support &amp; Maintenance'!$I$18</f>
+        <f>SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
       <c r="D28" s="20">
-        <f>'Support &amp; Maintenance'!$I$18</f>
+        <f>SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>'Support &amp; Maintenance'!$I$18</f>
+        <f>SUM('Support &amp; Maintenance'!$D$18:$G$18)</f>
         <v/>
       </c>
     </row>
@@ -6098,7 +6097,7 @@
         </is>
       </c>
       <c r="J22" s="33">
-        <f>SUM(J6:J21)</f>
+        <f>SUM(J6:J20)</f>
         <v/>
       </c>
     </row>
@@ -7075,7 +7074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7608,9 +7607,9 @@
       <c r="A28" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Activity Hazard Analysis (AHA)</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -7619,19 +7618,28 @@
         </is>
       </c>
       <c r="D28" s="11" t="n"/>
-      <c r="E28" s="33">
-        <f>SUM(E5:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="34">
-        <f>SUM(F5:F27)</f>
-        <v/>
-      </c>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="11" t="n"/>
       <c r="G28" s="11" t="n"/>
       <c r="H28" s="11" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E30" s="33">
+        <f>SUM(E5:E28)</f>
+        <v/>
+      </c>
+      <c r="F30" s="34">
+        <f>SUM(F5:F28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>The RDHX scope (§7.2) is a mechanical contractor's work, not a storage OEM's. Identify the partner and price it before bid, including BACnet/IP integration and leak-detection commissioning.</t>
         </is>
@@ -7733,7 +7741,7 @@
       </c>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>Nearline capacity heavily booked through 2026; CMR SKUs are a shrinking share of production as vendors shift to HAMR/SMR</t>
         </is>
@@ -7757,7 +7765,7 @@
       </c>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
-      <c r="F6" s="42" t="inlineStr">
+      <c r="F6" s="41" t="inlineStr">
         <is>
           <t>NAND allocation and pricing pressure through 2026; the RFP itself cites long lead times for memory technologies</t>
         </is>
@@ -7781,7 +7789,7 @@
       </c>
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
-      <c r="F7" s="42" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>SED/FIPS SKUs historically trail the leading capacity by a generation</t>
         </is>
@@ -7805,7 +7813,7 @@
       </c>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
-      <c r="F8" s="42" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>Memory market conditions cited in §1</t>
         </is>
@@ -7829,7 +7837,7 @@
       </c>
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n"/>
-      <c r="F9" s="42" t="inlineStr">
+      <c r="F9" s="41" t="inlineStr">
         <is>
           <t>Fabric choice may be gated on the SPECTRE-1 compute award</t>
         </is>
@@ -7853,7 +7861,7 @@
       </c>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n"/>
-      <c r="F10" s="42" t="inlineStr">
+      <c r="F10" s="41" t="inlineStr">
         <is>
           <t>Early-generation availability and firmware maturity in 2026–27</t>
         </is>
@@ -7877,7 +7885,7 @@
       </c>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n"/>
-      <c r="F11" s="42" t="inlineStr">
+      <c r="F11" s="41" t="inlineStr">
         <is>
           <t>Platform generation transition</t>
         </is>
@@ -7901,7 +7909,7 @@
       </c>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="42" t="inlineStr">
+      <c r="F12" s="41" t="inlineStr">
         <is>
           <t>Non-standard PDU spec per §7.1</t>
         </is>
@@ -7925,7 +7933,7 @@
       </c>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
-      <c r="F13" s="42" t="inlineStr">
+      <c r="F13" s="41" t="inlineStr">
         <is>
           <t>Custom spec: 1in sanitary, BACnet/IP, leak detect w/ shutdown, fail-closed</t>
         </is>
@@ -7949,7 +7957,7 @@
       </c>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
-      <c r="F14" s="42" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>§3.1.4 forbids passive copper DAC between cabinets</t>
         </is>
